--- a/XmlData/Datas/__enums__.xlsx
+++ b/XmlData/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DBEC75-00E8-4CAE-8AF8-D88A0AEA32E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4980" yWindow="2940" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -64,37 +64,68 @@
     <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
   </si>
   <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
+    <t>Enum.CheeseWord</t>
+  </si>
+  <si>
+    <t>Subject</t>
+  </si>
+  <si>
+    <t>Predicate</t>
+  </si>
+  <si>
+    <t>Object</t>
+  </si>
+  <si>
+    <t>Copula</t>
+  </si>
+  <si>
+    <t>Predicative</t>
+  </si>
+  <si>
+    <t>主语</t>
+  </si>
+  <si>
+    <t>谓语</t>
+  </si>
+  <si>
+    <t>宾语</t>
+  </si>
+  <si>
+    <t>系语</t>
+  </si>
+  <si>
+    <t>表语</t>
+  </si>
+  <si>
+    <t>usually verbs</t>
+  </si>
+  <si>
+    <t>linking verbs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -141,7 +172,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -154,9 +185,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -429,21 +463,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.875" customWidth="1"/>
-    <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
-    <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -473,7 +507,7 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +533,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="99" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -509,31 +543,91 @@
       <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="H5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="H6" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="I6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="H7" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7">
+        <v>4</v>
+      </c>
+      <c r="K7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/XmlData/Datas/__enums__.xlsx
+++ b/XmlData/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7DBEC75-00E8-4CAE-8AF8-D88A0AEA32E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD30626D-F4C0-4394-B9CE-F8448D9E1157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="2940" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
   </si>
   <si>
-    <t>Enum.CheeseWord</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -101,6 +98,9 @@
   </si>
   <si>
     <t>linking verbs</t>
+  </si>
+  <si>
+    <t>Enum.CheeseWordData</t>
   </si>
 </sst>
 </file>
@@ -182,11 +182,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,7 +466,7 @@
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.85546875" customWidth="1"/>
     <col min="4" max="5" width="14.140625" customWidth="1"/>
     <col min="6" max="6" width="9.42578125" customWidth="1"/>
@@ -499,13 +499,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
@@ -555,7 +555,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="B4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C4" t="b">
         <v>0</v>
@@ -564,35 +564,35 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="H5" s="4" t="s">
-        <v>16</v>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6">
         <v>3</v>
@@ -600,24 +600,24 @@
     </row>
     <row r="7" spans="1:12">
       <c r="H7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7">
         <v>4</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J8">
         <v>5</v>

--- a/XmlData/Datas/__enums__.xlsx
+++ b/XmlData/Datas/__enums__.xlsx
@@ -1,26 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD30626D-F4C0-4394-B9CE-F8448D9E1157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF7AC7C-CB7D-41A5-858B-DC48A9EE7AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4845" yWindow="3255" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -101,6 +106,12 @@
   </si>
   <si>
     <t>Enum.CheeseWordData</t>
+  </si>
+  <si>
+    <t>Adjective</t>
+  </si>
+  <si>
+    <t>Verb</t>
   </si>
 </sst>
 </file>
@@ -463,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -623,6 +634,22 @@
         <v>5</v>
       </c>
     </row>
+    <row r="9" spans="1:12">
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="H10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>

--- a/XmlData/Datas/__enums__.xlsx
+++ b/XmlData/Datas/__enums__.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Emil\Desktop\projects\GGJ2026\XmlData\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yinya\Documents\unityProjects\GGJ2026\XmlData\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF7AC7C-CB7D-41A5-858B-DC48A9EE7AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9280850-D6D4-48CC-BAE9-BD63B2475DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4845" yWindow="3255" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="-1210" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -112,6 +107,15 @@
   </si>
   <si>
     <t>Verb</t>
+  </si>
+  <si>
+    <t>Enum.DialogType</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Right</t>
   </si>
 </sst>
 </file>
@@ -140,7 +144,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -150,6 +154,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79995117038483843"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -183,7 +193,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -198,6 +208,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -564,23 +577,23 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="B4" t="s">
+    <row r="4" spans="1:12" s="5" customFormat="1">
+      <c r="B4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C4" t="b">
+      <c r="C4" s="5" t="b">
         <v>0</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="5" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="5">
         <v>1</v>
       </c>
     </row>
@@ -648,6 +661,31 @@
       </c>
       <c r="J10">
         <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" s="5" customFormat="1">
+      <c r="B12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="H13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
